--- a/src/订单/单子-姚足球-V4/result/lstm.xlsx
+++ b/src/订单/单子-姚足球-V4/result/lstm.xlsx
@@ -472,28 +472,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70.93650651210555</v>
+        <v>30.8826077903809</v>
       </c>
       <c r="B2" t="n">
-        <v>56.70400930433419</v>
+        <v>21.52174053863065</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9023430875624162</v>
+        <v>0.981490643160943</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01635874358343404</v>
+        <v>0.006030172752648867</v>
       </c>
       <c r="E2" t="n">
-        <v>42.04745690987114</v>
+        <v>41.39522061297634</v>
       </c>
       <c r="F2" t="n">
-        <v>30.27883591061091</v>
+        <v>32.86728167289188</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9933677877402209</v>
+        <v>0.9935719484390846</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006856000013034482</v>
+        <v>0.007290905432946819</v>
       </c>
     </row>
   </sheetData>
